--- a/Assets/Configs/DataTables/Datas/__tables__.xlsx
+++ b/Assets/Configs/DataTables/Datas/__tables__.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -121,6 +121,18 @@
   </si>
   <si>
     <t>CharacterInfo.xlsx</t>
+  </si>
+  <si>
+    <t>Battle.TbGuide</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle.Guide</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideInfo.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -463,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -591,6 +603,20 @@
         <v>32</v>
       </c>
     </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
